--- a/A_2018/chrI:46043-138130_612_finemapping.xlsx
+++ b/A_2018/chrI:46043-138130_612_finemapping.xlsx
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">61/253</t>
   </si>
   <si>
-    <t xml:space="preserve">327/2047</t>
+    <t xml:space="preserve">335/2047</t>
   </si>
   <si>
     <t xml:space="preserve">YBL068W/YBL011W/YBR003W/YBR052C/YBR117C/YBR159W/YDL078C/YDL052C/YDR001C/YDR148C/YDR232W/YDR234W/YDR300C/YDR321W/YDR399W/YDR487C/YDR503C/YEL011W/YER005W/YER141W/YFR015C/YFR055W/YGL205W/YGL148W/YGL012W/YGR088W/YGR175C/YGR255C/YHL011C/YHR174W/YIL162W/YIL160C/YIL155C/YJL097W/YJR019C/YKL181W/YKR067W/YLR056W/YLR100W/YLR142W/YLR258W/YLR372W/YLR450W/YML126C/YML056C/YML008C/YMR105C/YMR220W/YMR250W/YNL274C/YNL104C/YNL009W/YNR016C/YNR041C/YOL126C/YOR095C/YOR175C/YOR176W/YOR274W/YPL172C/YPR184W</t>
@@ -76938,10 +76938,10 @@
         <v>0.000000350832153394623</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0000315748938055161</v>
+        <v>0.0000319257259589107</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000029543760285863</v>
+        <v>0.0000299130572894363</v>
       </c>
       <c r="J2" t="s">
         <v>612</v>
@@ -76973,10 +76973,10 @@
         <v>0.00000104556667190407</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0000470505002356831</v>
+        <v>0.0000475732835716351</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000044023859869645</v>
+        <v>0.0000445741581180156</v>
       </c>
       <c r="J3" t="s">
         <v>619</v>
@@ -77005,13 +77005,13 @@
         <v>623</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000213478865363535</v>
+        <v>0.00043682746034753</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00640436596090606</v>
+        <v>0.0132504329638751</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00599238920318696</v>
+        <v>0.0124150962414561</v>
       </c>
       <c r="J4" t="s">
         <v>624</v>
@@ -77043,10 +77043,10 @@
         <v>0.00090519912570769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.020366980328423</v>
+        <v>0.0205932801098499</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0190568236991093</v>
+        <v>0.0192950339953481</v>
       </c>
       <c r="J5" t="s">
         <v>631</v>
@@ -77078,10 +77078,10 @@
         <v>0.00162601423884095</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0292682562991371</v>
+        <v>0.0295934591469053</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0273855029699528</v>
+        <v>0.0277278217570772</v>
       </c>
       <c r="J6" t="s">
         <v>637</v>
@@ -77113,10 +77113,10 @@
         <v>0.00213424983853588</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0320137475780383</v>
+        <v>0.0323694558844609</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0299543836987492</v>
+        <v>0.0303288134949836</v>
       </c>
       <c r="J7" t="s">
         <v>642</v>
